--- a/public/files/beneficiaries_sample.xlsx
+++ b/public/files/beneficiaries_sample.xlsx
@@ -1,37 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28919"/>
-  <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="28" documentId="11_D5CEDCC997D9AEAF821EA7EDBC2B8ECE5AB09F2F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7993E84F-A7F8-433A-B132-B9CE7E4A40A2}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user H\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5493F26-68E1-4C2B-9570-B5A84977CCCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Course Students" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="37">
   <si>
     <t>name</t>
   </si>
@@ -42,93 +31,119 @@
     <t>identity_number</t>
   </si>
   <si>
+    <t>phone</t>
+  </si>
+  <si>
     <t>birth_date</t>
   </si>
   <si>
-    <t>phone</t>
-  </si>
-  <si>
-    <t>gender</t>
+    <t>registered</t>
+  </si>
+  <si>
+    <t>certificate</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>relevance_identity</t>
+  </si>
+  <si>
+    <t>transportation</t>
+  </si>
+  <si>
+    <t>prev_exper</t>
   </si>
   <si>
     <t>address</t>
   </si>
   <si>
-    <t>فهد العتيبي</t>
-  </si>
-  <si>
-    <t>test@test.com</t>
-  </si>
-  <si>
-    <t>1023456789</t>
-  </si>
-  <si>
-    <t>male</t>
+    <t>request_certificate</t>
+  </si>
+  <si>
+    <t>email_certificate</t>
+  </si>
+  <si>
+    <t>أحمد محمد</t>
+  </si>
+  <si>
+    <t>ahmed@example.com</t>
+  </si>
+  <si>
+    <t>1234567890</t>
+  </si>
+  <si>
+    <t>0551234567</t>
+  </si>
+  <si>
+    <t>1990-01-01</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>مهتم بالدورة</t>
+  </si>
+  <si>
+    <t>مناسب</t>
+  </si>
+  <si>
+    <t>دورة سابقة</t>
+  </si>
+  <si>
+    <t>نعم لدي خبرة</t>
   </si>
   <si>
     <t>الرياض</t>
   </si>
   <si>
-    <t>نورة السبيعي</t>
-  </si>
-  <si>
-    <t>m@m.com</t>
-  </si>
-  <si>
-    <t>1098765432</t>
-  </si>
-  <si>
-    <t>female</t>
+    <t>سارة علي</t>
+  </si>
+  <si>
+    <t>sara@example.com</t>
+  </si>
+  <si>
+    <t>0987654321</t>
+  </si>
+  <si>
+    <t>0557654321</t>
+  </si>
+  <si>
+    <t>1992-05-10</t>
+  </si>
+  <si>
+    <t>طالبة جامعية</t>
+  </si>
+  <si>
+    <t>مرتبط جزئياً</t>
+  </si>
+  <si>
+    <t>لا يوجد</t>
+  </si>
+  <si>
+    <t>خبرة بسيطة</t>
   </si>
   <si>
     <t>جدة</t>
   </si>
   <si>
-    <t>خالد الزهراني</t>
-  </si>
-  <si>
-    <t>x@x.com</t>
-  </si>
-  <si>
-    <t>1011122233</t>
-  </si>
-  <si>
-    <t>الدمام</t>
+    <t xml:space="preserve">courses_before  </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -139,7 +154,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -147,37 +162,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -194,9 +186,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -234,7 +226,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -268,7 +260,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -303,10 +294,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -480,111 +470,151 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="4" max="4" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5703125" bestFit="1" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:O3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>8</v>
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="4">
-        <v>32947</v>
-      </c>
-      <c r="E2">
-        <v>514789258</v>
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G2" t="s">
-        <v>11</v>
+        <v>20</v>
+      </c>
+      <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>13</v>
+        <v>26</v>
+      </c>
+      <c r="B3" t="s">
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="4">
-        <v>31340</v>
-      </c>
-      <c r="E3">
-        <v>514789266</v>
+        <v>28</v>
+      </c>
+      <c r="D3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" t="s">
+        <v>30</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="4">
-        <v>34889</v>
-      </c>
-      <c r="E4" s="2">
-        <v>514789255</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="H3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K3" t="s">
         <v>20</v>
+      </c>
+      <c r="L3" t="s">
+        <v>34</v>
+      </c>
+      <c r="M3" t="s">
+        <v>35</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{64FD9454-B7F8-4E09-B83E-C9BCB33C323D}"/>
-    <hyperlink ref="B3" r:id="rId2" xr:uid="{FFEE7F2C-0BF1-4ECF-8BA1-2680895015D6}"/>
-    <hyperlink ref="B4" r:id="rId3" xr:uid="{997A95BB-7496-4FF2-B992-3FF764BA05C5}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>